--- a/reports/hazop_system_20.xlsx
+++ b/reports/hazop_system_20.xlsx
@@ -468,7 +468,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>HAZOP preparation — System 20</t>
+          <t>HAZOP preparation — System 20 (functional loops)</t>
         </is>
       </c>
     </row>
@@ -662,16 +662,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -711,15 +714,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -748,7 +766,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -777,7 +798,10 @@
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -806,7 +830,10 @@
       </c>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -835,7 +862,10 @@
       </c>
       <c r="E7" s="6" t="inlineStr"/>
       <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -852,16 +882,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -901,15 +934,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -938,7 +986,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -967,7 +1018,10 @@
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -984,16 +1038,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1033,15 +1090,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1070,7 +1142,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1099,7 +1174,10 @@
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1116,16 +1194,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1165,15 +1246,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1202,7 +1298,10 @@
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1231,7 +1330,10 @@
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1248,16 +1350,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="52" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1297,15 +1402,30 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Risk</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Action party</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1329,12 +1449,15 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>20-XV2202A, 20-XV2202B</t>
+          <t>20-XV2202A (⚠ same loop — verify independence), 20-XV2202B (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1358,12 +1481,15 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>20-XV2202A, 20-XV2202B</t>
+          <t>20-XV2202A (⚠ same loop — verify independence), 20-XV2202B (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1387,12 +1513,15 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>20-XV2202A, 20-XV2202B</t>
+          <t>20-XV2202A (⚠ same loop — verify independence), 20-XV2202B (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
@@ -1416,12 +1545,15 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>20-XV2202A, 20-XV2202B</t>
+          <t>20-XV2202A (⚠ same loop — verify independence), 20-XV2202B (⚠ same loop — verify independence)</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr"/>
       <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
